--- a/docs/sample_data/attendance_sample.xlsx
+++ b/docs/sample_data/attendance_sample.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,12 +441,17 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Mathematics</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Physics</t>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Geography</t>
         </is>
       </c>
     </row>
@@ -458,32 +463,50 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1</v>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SU2026-0001</t>
+          <t>SU2026-0002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -494,104 +517,617 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SU2026-0003</t>
+          <t>SU2026-0010</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SU2026-0009</t>
+          <t>SU2026-0014</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SU2026-0009</t>
+          <t>SU2026-0001</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SU2026-0010</t>
+          <t>SU2026-0002</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1</v>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>SU2026-0003</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>SU2026-0010</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SU2026-0014</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SU2026-0001</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SU2026-0002</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SU2026-0003</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SU2026-0010</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SU2026-0014</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SU2026-0001</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SU2026-0002</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SU2026-0003</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SU2026-0010</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SU2026-0014</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SU2026-0001</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SU2026-0002</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SU2026-0003</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SU2026-0010</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SU2026-0014</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
       </c>
     </row>
   </sheetData>
